--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N97_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N97_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.91926679768035</v>
+        <v>11.36188085462306</v>
       </c>
       <c r="D2" t="n">
-        <v>53.70456795585044</v>
+        <v>8.726992292825697</v>
       </c>
       <c r="E2" t="n">
-        <v>9.025586085778205</v>
+        <v>1.466657738938959</v>
       </c>
       <c r="F2" t="n">
-        <v>2.698888184016731</v>
+        <v>0.4385693299027187</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.86809462612394</v>
+        <v>8.428565376745141</v>
       </c>
       <c r="D3" t="n">
-        <v>48.30679158781698</v>
+        <v>7.84985363302026</v>
       </c>
       <c r="E3" t="n">
-        <v>9.025586085778205</v>
+        <v>1.466657738938959</v>
       </c>
       <c r="F3" t="n">
-        <v>2.698888184016731</v>
+        <v>0.4385693299027187</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
